--- a/jobs_result.xlsx
+++ b/jobs_result.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060893&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060893&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53920991&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53920991&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073336&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073336&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54086907&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54086907&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54071377&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54071377&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54088123&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54088123&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54044494&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54044494&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -692,27 +692,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>차량용 S/W Test 자동화 개발(Python)</t>
+          <t>Linux/Unix 기반 개발자(경력) 모집 (c,python, go)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(주)링크제니시스</t>
+          <t>(주)지란지교에스앤씨</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>인천서구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>~ 08/03(월)</t>
+          <t>~ 06/28(일)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078638&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026578&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -724,27 +724,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(주35시간)AI서비스 운영 개발자(Python/Docker/Linux)채용</t>
+          <t>차량용 S/W Test 자동화 개발(Python)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(주)브로드씨엔에스</t>
+          <t>(주)링크제니시스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>서울구로구</t>
+          <t>인천서구</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>~ 06/14(일)</t>
+          <t>~ 08/03(월)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54045566&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078638&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -756,27 +756,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[코레이즈]Python(Flask) 웹 개발자 채용 (신입, 보충역)</t>
+          <t>(주35시간)AI서비스 운영 개발자(Python/Docker/Linux)채용</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(주)코레이즈홀딩스</t>
+          <t>(주)브로드씨엔에스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>서울구로구</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>~ 06/14(일)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53835293&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54045566&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>화장품 스마트팩토리 MES,ERP,Pythonphp 개발자</t>
+          <t>[코레이즈]Python(Flask) 웹 개발자 채용 (신입, 보충역)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(주)아주화장품</t>
+          <t>(주)코레이즈홀딩스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>인천남동구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>~ 06/19(금)</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53943859&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53835293&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -820,27 +820,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vision AI 및 서버 솔루션 엔지니어 (Python, PyTorch, FastAPI)</t>
+          <t>화장품 스마트팩토리 MES,ERP,Pythonphp 개발자</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(주)흑자</t>
+          <t>(주)아주화장품</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>서울동대문구</t>
+          <t>인천남동구</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/19(금)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54017689&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53943859&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -852,27 +852,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[개발팀] 백엔드 개발자 (Python)</t>
+          <t>Vision AI 및 서버 솔루션 엔지니어 (Python, PyTorch, FastAPI)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(주)크리에이트크루</t>
+          <t>(주)흑자</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울동대문구</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>~ 06/19(금)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948095&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54017689&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -884,27 +884,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>국가 R&amp;D 연구과제 수행 / 데이터 분석 /python채용공고</t>
+          <t>[개발팀] 백엔드 개발자 (Python)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(재)국제도시물정보과학연구원</t>
+          <t>(주)크리에이트크루</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>인천남동구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>~ 06/28(일)</t>
+          <t>~ 06/19(금)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54022705&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948095&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -916,27 +916,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엠케이디PythonAI 개발자 채용 (경력 또는 석/박사)</t>
+          <t>국가 R&amp;D 연구과제 수행 / 데이터 분석 /python채용공고</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(주)엠케이디</t>
+          <t>(재)국제도시물정보과학연구원</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>부산남구</t>
+          <t>인천남동구</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/28(일)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53580217&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54022705&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[서울 문정] [경력3년이상 4,300~8,500] C++,Python백엔드개발</t>
+          <t>엠케이디PythonAI 개발자 채용 (경력 또는 석/박사)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(주)빅앤딥</t>
+          <t>(주)엠케이디</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>부산남구</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>~ 07/26(일)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999668&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53580217&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Python기반 자동화엔지니어 경력</t>
+          <t>[서울 문정] [경력3년이상 4,300~8,500] C++,Python백엔드개발</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(주)모두모아컴퍼니</t>
+          <t>(주)빅앤딥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>~ 06/13(토)</t>
+          <t>~ 07/26(일)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53904602&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999668&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1012,27 +1012,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>프타 솔루션 JAVA / DBA / TA / AA /PYTHONRecruitment</t>
+          <t>Python기반 자동화엔지니어 경력</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>플러거</t>
+          <t>(주)모두모아컴퍼니</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>서울구로구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>~ 06/13(토)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53849084&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53904602&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1044,17 +1044,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[이수그룹 IT계열사]Python개발자 채용</t>
+          <t>프타 솔루션 JAVA / DBA / TA / AA /PYTHONRecruitment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(주)이수시스템</t>
+          <t>플러거</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울구로구</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53846395&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53849084&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (React / TypeScript /Python) 채용</t>
+          <t>[이수그룹 IT계열사]Python개발자 채용</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(주)에스에이치엠디</t>
+          <t>(주)이수시스템</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>~ 06/11(목)</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53601949&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53846395&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1108,27 +1108,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[GSF솔루션] 스마트제조 SW개발자 채용(Python, AI)</t>
+          <t>Full-Stack Developer (React / TypeScript /Python) 채용</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(주)지에스에프솔루션</t>
+          <t>(주)에스에이치엠디</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>~ 06/11(목)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53853846&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53601949&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1140,27 +1140,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>생성형 AI 빅데이터 마케팅 플랫폼 데이터엔지니어(python)채용</t>
+          <t>[GSF솔루션] 스마트제조 SW개발자 채용(Python, AI)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(주)빅링크에이아이</t>
+          <t>(주)지에스에프솔루션</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004173&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53853846&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1172,27 +1172,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>oo기업 생성형 AI Agent 서비스 구축 /Python/ 시청</t>
+          <t>생성형 AI 빅데이터 마케팅 플랫폼 데이터엔지니어(python)채용</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(주)이에스티소프트</t>
+          <t>(주)빅링크에이아이</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>서울중구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>~ 06/08(월)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060443&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004173&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1204,27 +1204,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Flutter, PHP 또는Python2년 이상 실무 개발자</t>
+          <t>oo기업 생성형 AI Agent 서비스 구축 /Python/ 시청</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>글로벌엠아이지</t>
+          <t>(주)이에스티소프트</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>서울중구</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>~ 06/21(일)</t>
+          <t>~ 06/08(월)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53654598&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060443&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1236,27 +1236,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PythonBackend 개발자 채용(대전 연구소)</t>
+          <t>Flutter, PHP 또는Python2년 이상 실무 개발자</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(주)알고리즘랩스</t>
+          <t>글로벌엠아이지</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>대전중구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>~ 07/07(화)</t>
+          <t>~ 06/21(일)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53831012&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53654598&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1268,27 +1268,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Python기반 AI 개발자 채용</t>
+          <t>PythonBackend 개발자 채용(대전 연구소)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(주)코마이크로시스템즈</t>
+          <t>(주)알고리즘랩스</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>경남진주시</t>
+          <t>대전중구</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>~ 07/07(화)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53933436&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53831012&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1300,27 +1300,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[데이터랩스] LLM을 위한Python개발 경력자 모집</t>
+          <t>Python기반 AI 개발자 채용</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(주)데이터랩스</t>
+          <t>(주)코마이크로시스템즈</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>서울강서구</t>
+          <t>경남진주시</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>~ 06/14(일)</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54033789&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53933436&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>(주)이노앱 IT개발·데이터(C/C++,Python, Claude) 채용 공고</t>
+          <t>[데이터랩스] LLM을 위한Python개발 경력자 모집</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(주)이노앱</t>
+          <t>(주)데이터랩스</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>세종특별자치시</t>
+          <t>서울강서구</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>~ 06/27(토)</t>
+          <t>~ 06/14(일)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016018&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54033789&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1364,27 +1364,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Python백엔드 개발자를 찾고 있어요</t>
+          <t>(주)이노앱 IT개발·데이터(C/C++,Python, Claude) 채용 공고</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(주)매도왕</t>
+          <t>(주)이노앱</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>세종특별자치시</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>~ 06/19(금)</t>
+          <t>~ 06/27(토)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53943774&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016018&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1396,27 +1396,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[지오스토리]Python, 웹 개발자 신입/경력직 채용</t>
+          <t>Python백엔드 개발자를 찾고 있어요</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(주)지오스토리</t>
+          <t>(주)매도왕</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>서울강서구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>~ 07/02(목)</t>
+          <t>~ 06/19(금)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54054406&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53943774&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1428,27 +1428,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 제어 SW 개발 (ROS2 / C++ /Python)</t>
+          <t>[지오스토리]Python, 웹 개발자 신입/경력직 채용</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(주)메가젠임플란트</t>
+          <t>(주)지오스토리</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>대구달성군</t>
+          <t>서울강서구</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>~ 06/25(목)</t>
+          <t>~ 07/02(목)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53988207&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54054406&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>정교하고 실행력 있는 엔지니어 (Python)</t>
+          <t>휴머노이드 로봇 제어 SW 개발 (ROS2 / C++ /Python)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>리메세(주)</t>
+          <t>(주)메가젠임플란트</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>서울마포구</t>
+          <t>대구달성군</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>~ 07/01(수)</t>
+          <t>~ 06/25(목)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54039791&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53988207&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1492,27 +1492,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Python기반 자연어처리(NLP) AI 개발자 경력직 채용</t>
+          <t>정교하고 실행력 있는 엔지니어 (Python)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(주)바이브컴퍼니</t>
+          <t>리메세(주)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>서울종로구</t>
+          <t>서울마포구</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>~ 07/01(수)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53849649&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54039791&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Linux/Unix 기반 개발자(경력) 모집 (c,python, go)</t>
+          <t>Python기반 자연어처리(NLP) AI 개발자 경력직 채용</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(주)지란지교에스앤씨</t>
+          <t>(주)바이브컴퍼니</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>서울종로구</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>~ 06/28(일)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026578&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53849649&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53850131&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53850131&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53917483&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53917483&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54024927&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54024927&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968107&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968107&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53820228&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53820228&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078931&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=64ae7ab7-2dad-4a2e-9283-a9a9feefa7af</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078931&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a8361ba1-ec48-42ce-a3e4-19900a1b0e04</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54027260&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54027260&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54011037&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54011037&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54058140&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54058140&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54011981&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54011981&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53876914&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53876914&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53986706&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53986706&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53862136&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53862136&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54074200&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54074200&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53979463&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53979463&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53790246&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53790246&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53929562&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53929562&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53821998&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53821998&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54037712&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54037712&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046417&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046417&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53847922&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53847922&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53990429&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53990429&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53987523&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53987523&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53986663&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53986663&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53902323&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53902323&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53584482&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53584482&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53621321&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53621321&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53970113&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53970113&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53978633&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53978633&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53978116&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53978116&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53584585&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53584585&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54056067&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54056067&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53989406&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53989406&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53851739&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53851739&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54035087&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54035087&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54024375&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54024375&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54069499&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54069499&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53981806&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53981806&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948054&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948054&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948041&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948041&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948069&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53948069&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53649317&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53649317&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53912926&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53912926&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53953111&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53953111&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004376&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004376&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53932070&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=7a97c066-6727-4491-857d-570d09a5f2b8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53932070&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=9090b8bc-54e3-47ba-b977-5fb3892bb6bb</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53789747&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53789747&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53887168&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53887168&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53900100&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53900100&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53660011&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53660011&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54023849&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54023849&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060781&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060781&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54090263&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54090263&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079627&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079627&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54071734&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54071734&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53489648&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53489648&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060583&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060583&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079696&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079696&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53965580&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53965580&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999283&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999283&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54055086&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54055086&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53947937&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53947937&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53789227&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53789227&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53934162&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53934162&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968177&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968177&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53817816&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53817816&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54003684&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54003684&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54000070&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54000070&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54027071&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54027071&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001715&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001715&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54025208&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54025208&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53996576&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53996576&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53770389&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53770389&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53996355&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53996355&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53861623&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53861623&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53930615&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53930615&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53263131&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53263131&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968419&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968419&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53187908&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53187908&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53556550&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53556550&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012314&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012314&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53903007&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53903007&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53964030&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53964030&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53930400&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53930400&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54030427&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54030427&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54029894&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=f19337c3-7ecf-43b3-a92e-9f54d4b9bfe9</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54029894&amp;location=ts&amp;searchword=python&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=93dcd452-9d4f-47cd-ba6d-f327ff3406eb</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53930400&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53930400&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54072725&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54072725&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54021370&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54021370&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53829201&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53829201&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53809649&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53809649&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53995507&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53995507&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54037824&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54037824&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54088323&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54088323&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54029618&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54029618&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53935132&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53935132&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004234&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004234&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54071635&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54071635&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53716025&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53716025&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54029371&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54029371&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079488&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079488&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54077506&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54077506&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53815009&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53815009&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54035011&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54035011&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54005304&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54005304&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54086746&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54086746&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53957977&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53957977&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53947929&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53947929&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085892&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085892&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54062995&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54062995&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001288&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001288&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54041224&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54041224&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078500&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078500&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54072676&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54072676&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5204,27 +5204,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>AI 엔지니어 (백엔드개발자)</t>
+          <t>백엔드개발자 모집</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>(주)두핸즈</t>
+          <t>에이엠스퀘어(주)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>경북포항시 남구</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>~ 07/01(수)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059120&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026980&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5236,27 +5236,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[ICT사업부] 프론트/백엔드/챗봇/인공지능 웹개발자 정규직 채용</t>
+          <t>AI 엔지니어 (백엔드개발자)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>(주)쿨스</t>
+          <t>(주)두핸즈</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>부산강서구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>~ 07/01(수)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53852365&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059120&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5268,27 +5268,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>백엔드개발자 모집</t>
+          <t>[ICT사업부] 프론트/백엔드/챗봇/인공지능 웹개발자 정규직 채용</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>(주)제주엔젤렌트카</t>
+          <t>(주)쿨스</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>제주제주시</t>
+          <t>부산강서구</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>~ 07/05(일)</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54090298&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53852365&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5300,27 +5300,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[비케이브] AX백엔드·데이터 엔지니어 경력채용</t>
+          <t>백엔드개발자 모집</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>(주)비케이브</t>
+          <t>(주)제주엔젤렌트카</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>서울마포구</t>
+          <t>제주제주시</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>~ 06/27(토)</t>
+          <t>~ 07/05(일)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53752057&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54090298&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5332,27 +5332,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[경력] JAVA  WEB/APP백엔드개발자</t>
+          <t>[비케이브] AX백엔드·데이터 엔지니어 경력채용</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>(주)인피아드</t>
+          <t>(주)비케이브</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>경기과천시</t>
+          <t>서울마포구</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/27(토)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53960167&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53752057&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5364,27 +5364,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[캐시워크]백엔드개발 채용전환형 인턴</t>
+          <t>[경력] JAVA  WEB/APP백엔드개발자</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>넛지헬스케어(주)</t>
+          <t>(주)인피아드</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기과천시</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53570573&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53960167&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5396,27 +5396,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>백엔드개발자</t>
+          <t>[캐시워크]백엔드개발 채용전환형 인턴</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>(주)와탭랩스</t>
+          <t>넛지헬스케어(주)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>~ 06/09(화)</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53872928&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53570573&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5428,27 +5428,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JAVA 기반백엔드개발자</t>
+          <t>백엔드개발자</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>(주)혁산정보시스템</t>
+          <t>(주)와탭랩스</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>~ 07/04(토)</t>
+          <t>~ 06/09(화)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54086458&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53872928&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5460,27 +5460,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>백엔드개발자 채용 (상현역/마곡역)</t>
+          <t>JAVA 기반백엔드개발자</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>(주)티윈</t>
+          <t>(주)혁산정보시스템</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>서울강서구</t>
+          <t>서울영등포구</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>~ 07/04(토)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54049497&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54086458&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>백엔드개발자 (경력 1년 이상)</t>
+          <t>백엔드개발자 채용 (상현역/마곡역)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>스페이스맵(주)</t>
+          <t>(주)티윈</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>서울강서구</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>~ 06/24(수)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53990460&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54049497&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5524,27 +5524,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>백엔드개발자 (경력)</t>
+          <t>백엔드개발자 (경력 1년 이상)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>(주)아인잡</t>
+          <t>스페이스맵(주)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>~ 06/26(금)</t>
+          <t>~ 06/24(수)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54000909&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53990460&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5556,12 +5556,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>[KB금융그룹 계열] KB헬스케어백엔드개발자 채용</t>
+          <t>백엔드개발자 (경력)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>(주)케이비헬스케어</t>
+          <t>(주)아인잡</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/26(금)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53886845&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=eab155e7-8b70-4929-865a-a3877e6057a8</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54000909&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3ebe2091-5dba-4a50-9127-3d61934a56dd</t>
         </is>
       </c>
     </row>
@@ -5588,27 +5588,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[에코마케팅]백엔드개발자(Java) 인턴/신입 채용</t>
+          <t>[KB금융그룹 계열] KB헬스케어백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>(주)에코마케팅</t>
+          <t>(주)케이비헬스케어</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999254&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53886845&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5620,27 +5620,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>(주)와이즈케어백엔드개발자 채용</t>
+          <t>[에코마케팅]백엔드개발자(Java) 인턴/신입 채용</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>(주)와이즈케어</t>
+          <t>(주)에코마케팅</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>~ 07/05(일)</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54084928&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999254&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5652,27 +5652,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>[신입/경력] JAVA, Node백엔드및 미들웨어 정규직 채용</t>
+          <t>(주)와이즈케어백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>브라더스비(주)</t>
+          <t>(주)와이즈케어</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>서울관악구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>~ 06/12(금)</t>
+          <t>~ 07/05(일)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53874847&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54084928&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5684,27 +5684,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[글로벌핀테크]백엔드웹 개발자 (Java/Spring) 경력직 채용</t>
+          <t>[신입/경력] JAVA, Node백엔드및 미들웨어 정규직 채용</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>(주)핀샷</t>
+          <t>브라더스비(주)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>서울마포구</t>
+          <t>서울관악구</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>~ 06/12(금)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53988252&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53874847&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5716,27 +5716,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>[ADQUA] Java백엔드웹개발자(3년이상 팀원)</t>
+          <t>[글로벌핀테크]백엔드웹 개발자 (Java/Spring) 경력직 채용</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>(주)애드쿠아인터렉티브</t>
+          <t>(주)핀샷</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울마포구</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53942418&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53988252&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5748,27 +5748,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>[대구] Java 자바백엔드개발자 채용</t>
+          <t>[ADQUA] Java백엔드웹개발자(3년이상 팀원)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>(주)드림아이디어소프트</t>
+          <t>(주)애드쿠아인터렉티브</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>대구동구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>~ 06/29(월)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53772508&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53942418&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5780,27 +5780,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>[다날핀테크]백엔드경력사원(5년 이상/팀장급) 채용</t>
+          <t>[대구] Java 자바백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>(주)다날핀테크</t>
+          <t>(주)드림아이디어소프트</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>대구동구</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/29(월)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53716150&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53772508&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5812,27 +5812,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>AI 에이전트 기반백엔드개발자 구인</t>
+          <t>[다날핀테크]백엔드경력사원(5년 이상/팀장급) 채용</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>(주)애나</t>
+          <t>(주)다날핀테크</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>서울종로구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53952175&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53716150&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5844,27 +5844,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>(신입/경력) 대구백엔드/인프라 개발자 모집합니다</t>
+          <t>AI 에이전트 기반백엔드개발자 구인</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>범호아이티(주)</t>
+          <t>(주)애나</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>대구동구</t>
+          <t>서울종로구</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>~ 06/22(월)</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53976479&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53952175&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5876,27 +5876,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[송도] AI 에이전트 기반백엔드개발자 구인</t>
+          <t>(신입/경력) 대구백엔드/인프라 개발자 모집합니다</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>(주)애나</t>
+          <t>범호아이티(주)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>인천연수구</t>
+          <t>대구동구</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>~ 06/22(월)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54036942&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53976479&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5908,27 +5908,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>(주)큐뱅 JAVA 기반백엔드개발자 채용 (경력)</t>
+          <t>[송도] AI 에이전트 기반백엔드개발자 구인</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>(주)큐뱅</t>
+          <t>(주)애나</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>인천연수구</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>~ 07/01(수)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54047573&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54036942&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5940,27 +5940,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>백엔드개발자 모집(주니어급)</t>
+          <t>(주)큐뱅 JAVA 기반백엔드개발자 채용 (경력)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>슈어테크 주식회사</t>
+          <t>(주)큐뱅</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>서울광진구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>~ 06/14(일)</t>
+          <t>~ 07/01(수)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53633704&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54047573&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -5972,27 +5972,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>[대전근무] B2B SaaS백엔드개발자 채용</t>
+          <t>연구개발(백엔드개발자) 채용</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>(주)엑소스피어랩스</t>
+          <t>슈어데이터랩(주)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>대전서구</t>
+          <t>대전유성구</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>~ 06/26(금)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53997053&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54090445&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6004,27 +6004,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>(주)메인 JAVA백엔드개발자 경력 채용 공고입니다</t>
+          <t>백엔드개발자 모집(주니어급)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>(주)메인</t>
+          <t>슈어테크 주식회사</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울광진구</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>~ 06/14(일)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53985707&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53633704&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6036,27 +6036,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>백엔드개발자 모집</t>
+          <t>[대전근무] B2B SaaS백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>(주)제이디원</t>
+          <t>(주)엑소스피어랩스</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>서울금천구</t>
+          <t>대전서구</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>~ 06/25(목)</t>
+          <t>~ 06/26(금)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53989728&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53997053&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>백엔드개발자 3년이상</t>
+          <t>(주)메인 JAVA백엔드개발자 경력 채용 공고입니다</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>(주)럭스로보</t>
+          <t>(주)메인</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>~ 07/01(수)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54054915&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53985707&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6100,27 +6100,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[5년 이상] AI 활용 및 개발이 가능한백엔드개발자 채용</t>
+          <t>백엔드개발자 모집</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>(주)유티이씨</t>
+          <t>(주)제이디원</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>서울금천구</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>~ 07/05(일)</t>
+          <t>~ 06/25(목)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54091087&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53989728&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6132,27 +6132,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>(주)모드파티에서 웹·백엔드개발자 모시고 있어요</t>
+          <t>백엔드개발자 3년이상</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>(주)모드파티</t>
+          <t>(주)럭스로보</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 07/01(수)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53553496&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54054915&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6164,27 +6164,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>(주)오티톤메디컬 어플리케이션백엔드개발자 채용해요</t>
+          <t>[5년 이상] AI 활용 및 개발이 가능한백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>(주)오티톤메디컬</t>
+          <t>(주)유티이씨</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>서울금천구</t>
+          <t>서울영등포구</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>~ 07/05(일)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53888150&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54091087&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6196,27 +6196,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>주식회사더와이드코넥트백엔드신입/인턴 개발자를 찾고 있어요</t>
+          <t>(주)모드파티에서 웹·백엔드개발자 모시고 있어요</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>주식회사더와이드코넥트(THEWIDECONNECTINC)</t>
+          <t>(주)모드파티</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53954067&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53553496&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6228,27 +6228,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>플랫폼 숏폼&amp;라이브[미디어&amp;스트리밍]백엔드개발자 도전</t>
+          <t>(주)오티톤메디컬 어플리케이션백엔드개발자 채용해요</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>케이엠에스대한민국산지직송(주)</t>
+          <t>(주)오티톤메디컬</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>부산부산진구</t>
+          <t>서울금천구</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>~ 07/28(화)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54027145&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53888150&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6260,27 +6260,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>모비고백엔드개발자 인턴 채용</t>
+          <t>주식회사더와이드코넥트백엔드신입/인턴 개발자를 찾고 있어요</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>모비고(주)</t>
+          <t>주식회사더와이드코넥트(THEWIDECONNECTINC)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54049928&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53954067&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6292,27 +6292,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[WAUG]와그백엔드개발자(PHP, JAVA) 모집</t>
+          <t>플랫폼 숏폼&amp;라이브[미디어&amp;스트리밍]백엔드개발자 도전</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>(주)와그</t>
+          <t>케이엠에스대한민국산지직송(주)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>서울종로구</t>
+          <t>부산부산진구</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>~ 07/01(수)</t>
+          <t>~ 07/28(화)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54039834&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54027145&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6324,27 +6324,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[통신사] STAGE FIVE '백엔드(노드)' 경력자 채용</t>
+          <t>모비고백엔드개발자 인턴 채용</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>(주)스테이지파이브</t>
+          <t>모비고(주)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046123&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54049928&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6356,27 +6356,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>(주)시그마커넥트 하계 방학 인턴백엔드개발자 채용 공고</t>
+          <t>[WAUG]와그백엔드개발자(PHP, JAVA) 모집</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>(주)시그마커넥트</t>
+          <t>(주)와그</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>서울강동구</t>
+          <t>서울종로구</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 07/01(수)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059448&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54039834&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6388,27 +6388,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>[메타크라우드]백엔드개발자 모집 (서울/선정릉, 1년~3년)</t>
+          <t>[통신사] STAGE FIVE '백엔드(노드)' 경력자 채용</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>(주)메타크라우드</t>
+          <t>(주)스테이지파이브</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>~ 07/02(목)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54061489&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046123&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6420,27 +6420,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>(주)알로이스 AWS백엔드개발자 경력 채용 공고</t>
+          <t>(주)시그마커넥트 하계 방학 인턴백엔드개발자 채용 공고</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>(주)알로이스</t>
+          <t>(주)시그마커넥트</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울강동구</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>~ 07/14(화)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53900428&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059448&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6452,27 +6452,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>함께하실 Backend(백엔드)개발자 모집합니다.</t>
+          <t>[메타크라우드]백엔드개발자 모집 (서울/선정릉, 1년~3년)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>주식회사슈튜(SyuTyu)</t>
+          <t>(주)메타크라우드</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>~ 07/02(목)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53853497&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54061489&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6484,27 +6484,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>글로벌 커머스백엔드개발자 채용 (AI 활용 역량 우대)</t>
+          <t>(주)알통백엔드개발자(경력직) 채용</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>루쿠쿠(주)</t>
+          <t>(주)알통</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>서울구로구</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>~ 06/26(금)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001646&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087703&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6516,27 +6516,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>[제너러티브랩] 졸업 &amp; 스펙 필요 없습니다. (백엔드엔지니어)</t>
+          <t>(주)알로이스 AWS백엔드개발자 경력 채용 공고</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>(주)제너러티브랩</t>
+          <t>(주)알로이스</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>서울성북구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>~ 07/14(화)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54002142&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53900428&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6548,27 +6548,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>(주)이진솔루션에서 JAVA백엔드개발자 채용해요</t>
+          <t>함께하실 Backend(백엔드)개발자 모집합니다.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>(주)이진솔루션</t>
+          <t>주식회사슈튜(SyuTyu)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>경남창원시 마산회원구</t>
+          <t>서울영등포구</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>~ 07/05(일)</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087708&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53853497&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6580,27 +6580,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>(주)나휴케어  15명모집(블록체인 &amp;Java백엔드개발자 모집)</t>
+          <t>글로벌 커머스백엔드개발자 채용 (AI 활용 역량 우대)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>(주)나휴케어</t>
+          <t>루쿠쿠(주)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>~ 06/26(금)</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53846229&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001646&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6612,27 +6612,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IT개발·데이터(백엔드/서버개발 외 1개 부문) 채용</t>
+          <t>[제너러티브랩] 졸업 &amp; 스펙 필요 없습니다. (백엔드엔지니어)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>(주)체인일렉트로닉스</t>
+          <t>(주)제너러티브랩</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>서울구로구</t>
+          <t>서울성북구</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53846300&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54002142&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6644,27 +6644,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>[셀파트너랩스] AI 커머스 스타트업에서백엔드/AI 모집합니다.</t>
+          <t>(주)이진솔루션에서 JAVA백엔드개발자 채용해요</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>(주)셀파트너랩스</t>
+          <t>(주)이진솔루션</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>서울용산구</t>
+          <t>경남창원시 마산회원구</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>~ 07/01(수)</t>
+          <t>~ 07/05(일)</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046727&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087708&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6676,27 +6676,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>[AI 헬스케어] 풀스택 개발자 채용(백엔드베이스)</t>
+          <t>(주)나휴케어  15명모집(블록체인 &amp;Java백엔드개발자 모집)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>크리스타비전(주)</t>
+          <t>(주)나휴케어</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>서울마포구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>~ 06/12(금)</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54025918&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53846229&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6708,27 +6708,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>[똑똑홀딩스 / 신논현역]백엔드개발자 경력직 채용</t>
+          <t>IT개발·데이터(백엔드/서버개발 외 1개 부문) 채용</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>(주)똑똑홀딩스</t>
+          <t>(주)체인일렉트로닉스</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울구로구</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53820053&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53846300&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6740,27 +6740,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>백엔드개발자 채용</t>
+          <t>[셀파트너랩스] AI 커머스 스타트업에서백엔드/AI 모집합니다.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>주식회사 원가람</t>
+          <t>(주)셀파트너랩스</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울용산구</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>~ 07/01(수)</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53816644&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046727&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6772,27 +6772,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AI 및 라이브 기반 반려동물 양육 플랫폼백엔드개발자 채용</t>
+          <t>[AI 헬스케어] 풀스택 개발자 채용(백엔드베이스)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>(주)플레이웍스</t>
+          <t>크리스타비전(주)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울마포구</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/12(금)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53915048&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54025918&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6804,27 +6804,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>[피스챌린지그룹]백엔드개발자 채용 (신입/경력)</t>
+          <t>[똑똑홀딩스 / 신논현역]백엔드개발자 경력직 채용</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>피스챌린지그룹(주)</t>
+          <t>(주)똑똑홀딩스</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>오늘마감</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53952994&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53820053&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6836,27 +6836,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IT개발·데이터(웹개발&amp;프론트엔드&amp;백엔드) 채용</t>
+          <t>백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>이크론소프트</t>
+          <t>주식회사 원가람</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>경남김해시</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>~ 06/12(금)</t>
+          <t>오늘마감</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999689&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=c2a637fb-709c-484e-9a5c-cf62aaa6e266</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53816644&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=3e95d173-337d-40ed-b277-a4aa5640191b</t>
         </is>
       </c>
     </row>
@@ -6868,27 +6868,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>[아랑소프트]SI개발&amp;웹개발&amp;백엔드/서버개발 외 정규직 채용</t>
+          <t>AI 및 라이브 기반 반려동물 양육 플랫폼백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>(주)아랑소프트</t>
+          <t>(주)플레이웍스</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>서울구로구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>~ 06/26(금)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999453&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53915048&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -6900,27 +6900,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>생성형 AI 빅데이터 마케팅 플랫폼백엔드(JAVA) 개발자 채용</t>
+          <t>[피스챌린지그룹]백엔드개발자 채용 (신입/경력)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>(주)빅링크에이아이</t>
+          <t>피스챌린지그룹(주)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004165&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53952994&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -6932,27 +6932,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>세무 ERP·세무플랫폼 구축백엔드/풀스택 개발자 채용</t>
+          <t>IT개발·데이터(웹개발&amp;프론트엔드&amp;백엔드) 채용</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>(주)비앤씨파트너스</t>
+          <t>이크론소프트</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>경남김해시</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>~ 07/27(월)</t>
+          <t>~ 06/12(금)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010736&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999689&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -6964,17 +6964,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>서버백엔드개발자 채용</t>
+          <t>[아랑소프트]SI개발&amp;웹개발&amp;백엔드/서버개발 외 정규직 채용</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>(주)머니무브</t>
+          <t>(주)아랑소프트</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울구로구</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001340&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53999453&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>백엔드개발자 경력 채용</t>
+          <t>생성형 AI 빅데이터 마케팅 플랫폼백엔드(JAVA) 개발자 채용</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>스트라토</t>
+          <t>(주)빅링크에이아이</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53578867&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004165&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7028,27 +7028,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AI 플랫폼백엔드개발자(전문연구요원 가능)</t>
+          <t>세무 ERP·세무플랫폼 구축백엔드/풀스택 개발자 채용</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>(주)트윔</t>
+          <t>(주)비앤씨파트너스</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>경기화성시</t>
+          <t>서울영등포구</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>~ 07/27(월)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54076549&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010736&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7060,27 +7060,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>[대전]공공 교통안전 시스템 구축 관련 웹/백엔드경력 개발</t>
+          <t>서버백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>(주)이웃</t>
+          <t>(주)머니무브</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>대전중구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>~ 07/05(일)</t>
+          <t>~ 06/26(금)</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54084738&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54001340&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7092,27 +7092,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>(부산) (주)일루넥스 웹 프로그래머(백엔드) 경력직 채용-팀장급</t>
+          <t>백엔드개발자 경력 채용</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>일루넥스</t>
+          <t>스트라토</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>부산남구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073951&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53578867&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7124,27 +7124,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>풀스택/백엔드개발자 채용 (마이크로바이옴 플랫폼 고도화)</t>
+          <t>AI 플랫폼백엔드개발자(전문연구요원 가능)</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>(주)인크로비</t>
+          <t>(주)트윔</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>서울금천구</t>
+          <t>경기화성시</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>~ 07/11(토)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53865000&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54076549&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7156,27 +7156,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>백엔드개발자(JAVA) 신입 및 경력 모집</t>
+          <t>[대전]공공 교통안전 시스템 구축 관련 웹/백엔드경력 개발</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>(주)제온스</t>
+          <t>(주)이웃</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>대전중구</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 07/05(일)</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53859869&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54084738&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7188,27 +7188,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>백엔드개발자 경력 채용</t>
+          <t>(부산) (주)일루넥스 웹 프로그래머(백엔드) 경력직 채용-팀장급</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>(주)씨어스</t>
+          <t>일루넥스</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>부산남구</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>~ 06/27(토)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010132&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073951&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7220,27 +7220,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>백엔드개발자 모집</t>
+          <t>[AI 클라우드 SW]백엔드/프론트엔드/앱 개발자 채용</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>(주)아이스크림미디어</t>
+          <t>(주)인티그리트</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>~ 06/27(토)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53749052&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53860741&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7252,27 +7252,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Java백엔드개발자 [경력 3~8년]</t>
+          <t>풀스택/백엔드개발자 채용 (마이크로바이옴 플랫폼 고도화)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>(주)제네시스네스트</t>
+          <t>(주)인크로비</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>경기용인시 수지구</t>
+          <t>서울금천구</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>~ 07/02(목)</t>
+          <t>~ 07/11(토)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059841&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53865000&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7284,27 +7284,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>[쿠도커뮤니케이션] AX사업부 AX엔지니어링팀백엔드개발자 채용</t>
+          <t>백엔드개발자(JAVA) 신입 및 경력 모집</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>쿠도커뮤니케이션(주)</t>
+          <t>(주)제온스</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>경기과천시</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>~ 07/04(토)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078811&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53859869&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7316,27 +7316,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>원스토어 개발자 채용 (백엔드&amp;프론트엔드)</t>
+          <t>백엔드개발자 경력 채용</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>원스토어(주)</t>
+          <t>(주)씨어스</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>경기과천시</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>~ 06/14(일)</t>
+          <t>~ 06/27(토)</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53984724&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010132&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7348,27 +7348,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>[AI서비스]백엔드개발 경력직 채용</t>
+          <t>백엔드개발자 모집</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>(주)솔트룩스</t>
+          <t>(주)아이스크림미디어</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/27(토)</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53581891&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53749052&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7380,27 +7380,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>[하이브랩] Java / Spring백엔드개발자 채용 (6년 이상)</t>
+          <t>Java백엔드개발자 [경력 3~8년]</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>(주)하이브랩</t>
+          <t>(주)제네시스네스트</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>경기용인시 수지구</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>~ 06/13(토)</t>
+          <t>~ 07/02(목)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53887735&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059841&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7412,27 +7412,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>[다우키움 계열사] 숏폼 플랫폼백엔드개발자 (7년 이상)</t>
+          <t>[쿠도커뮤니케이션] AX사업부 AX엔지니어링팀백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>(주)키다리스튜디오</t>
+          <t>쿠도커뮤니케이션(주)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>경기과천시</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>~ 06/28(일)</t>
+          <t>~ 07/04(토)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026738&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078811&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7444,27 +7444,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>[다우키움 계열사] 사내 정산 시스템백엔드개발자 (7년 이상)</t>
+          <t>원스토어 개발자 채용 (백엔드&amp;프론트엔드)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>(주)키다리스튜디오</t>
+          <t>원스토어(주)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>경기과천시</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>~ 06/28(일)</t>
+          <t>~ 06/14(일)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026648&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53984724&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7476,27 +7476,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>[다우키움 계열사] AI 활용 시스템백엔드개발자 (경력)</t>
+          <t>[AI서비스]백엔드개발 경력직 채용</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>(주)키다리스튜디오</t>
+          <t>(주)솔트룩스</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>~ 06/28(일)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026685&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53581891&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7508,27 +7508,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>[텔코웨어]  Java백엔드개발 경력사원 채용공고</t>
+          <t>[하이브랩] Java / Spring백엔드개발자 채용 (6년 이상)</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>텔코웨어(주)</t>
+          <t>(주)하이브랩</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>~ 07/12(일)</t>
+          <t>~ 06/13(토)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53873236&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53887735&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7540,27 +7540,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>[로보티즈AI] 자율주행로봇 시스템백엔드개발자</t>
+          <t>[다우키움 계열사] 숏폼 플랫폼백엔드개발자 (7년 이상)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>(주)로보티즈</t>
+          <t>(주)키다리스튜디오</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>서울강서구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>~ 07/17(금)</t>
+          <t>~ 06/28(일)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53923158&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026738&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>백엔드엔지니어 (시니어)</t>
+          <t>[다우키움 계열사] 사내 정산 시스템백엔드개발자 (7년 이상)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>위즈코어(주)</t>
+          <t>(주)키다리스튜디오</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>~ 06/21(일)</t>
+          <t>~ 06/28(일)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968606&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026648&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7604,27 +7604,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>[VIRNECT]백엔드개발자 채용</t>
+          <t>[다우키움 계열사] AI 활용 시스템백엔드개발자 (경력)</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>주식회사 버넥트</t>
+          <t>(주)키다리스튜디오</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>서울용산구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>~ 07/04(토)</t>
+          <t>~ 06/28(일)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54074299&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026685&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7636,27 +7636,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>백엔드개발자</t>
+          <t>[텔코웨어]  Java백엔드개발 경력사원 채용공고</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>패스트레인(여신티켓)</t>
+          <t>텔코웨어(주)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>~ 07/12(일)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53834438&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53873236&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7668,27 +7668,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>백엔드개발자</t>
+          <t>[로보티즈AI] 자율주행로봇 시스템백엔드개발자</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>패스트레인(여신티켓)</t>
+          <t>(주)로보티즈</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울강서구</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>진행예정</t>
+          <t>~ 07/17(금)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54090962&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53923158&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7700,27 +7700,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[송파/스타트업] 커머스사백엔드시스템 개발자 채용</t>
+          <t>백엔드엔지니어 (시니어)</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>(주)사람인에이치에스</t>
+          <t>위즈코어(주)</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/21(일)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53708686&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53968606&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7732,27 +7732,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>(주)에스비정보기술 인프라백엔드/프론트엔드 개발자 모집</t>
+          <t>[VIRNECT]백엔드개발자 채용</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>(주)에스비정보기술</t>
+          <t>주식회사 버넥트</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>경기의왕시</t>
+          <t>서울용산구</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>~ 07/03(금)</t>
+          <t>~ 07/04(토)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53786464&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54074299&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7764,27 +7764,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>프론트엔드/백엔드개발자 모집</t>
+          <t>백엔드개발자</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>(주)윈즈</t>
+          <t>패스트레인(여신티켓)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>~ 07/05(일)</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085112&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53834438&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7801,22 +7801,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>티엔에이치(주)</t>
+          <t>패스트레인(여신티켓)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>진행예정</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53863976&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54090962&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7828,27 +7828,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>백엔드개발자</t>
+          <t>[송파/스타트업] 커머스사백엔드시스템 개발자 채용</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>(주)필라넷</t>
+          <t>(주)사람인에이치에스</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53863954&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53708686&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7860,27 +7860,27 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>백엔드웹프로그래머 (4-7년)</t>
+          <t>(주)에스비정보기술 인프라백엔드/프론트엔드 개발자 모집</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>(주)키트웍스</t>
+          <t>(주)에스비정보기술</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>경기의왕시</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>~ 06/28(일)</t>
+          <t>~ 07/03(금)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54023961&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53786464&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7892,27 +7892,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>백엔드·인프라 풀스택 엔지니어</t>
+          <t>프론트엔드/백엔드개발자 모집</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>(주)베스텔라랩</t>
+          <t>(주)윈즈</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>경기안양시 동안구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>~ 07/02(목)</t>
+          <t>~ 07/05(일)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54062452&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085112&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7924,17 +7924,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>백엔드개발 엔지니어(backend)</t>
+          <t>백엔드개발자</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>(주)위펀</t>
+          <t>티엔에이치(주)</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53865325&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53863976&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7956,27 +7956,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>런드리24백엔드개발자</t>
+          <t>백엔드개발자</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>(주)의식주컴퍼니</t>
+          <t>(주)필라넷</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>경기군포시</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53967438&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53863954&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -7988,27 +7988,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>백엔드개발자(4~6년)</t>
+          <t>백엔드웹프로그래머 (4-7년)</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>(주)에스피코리아</t>
+          <t>(주)키트웍스</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>서울강서구</t>
+          <t>서울영등포구</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>~ 06/25(목)</t>
+          <t>~ 06/28(일)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53981282&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54023961&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -8020,27 +8020,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>백엔드개발자(1~3년)</t>
+          <t>백엔드·인프라 풀스택 엔지니어</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>(주)에스피코리아</t>
+          <t>(주)베스텔라랩</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>서울강서구</t>
+          <t>경기안양시 동안구</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>~ 06/25(목)</t>
+          <t>~ 07/02(목)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53981279&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54062452&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -8052,27 +8052,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>백엔드개발자 모집</t>
+          <t>백엔드개발 엔지니어(backend)</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>에이엠스퀘어(주)</t>
+          <t>(주)위펀</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>경북포항시 남구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54026980&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53865325&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -8084,27 +8084,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>병원용 AI Smart Desk 서비스백엔드/풀스택 경력개발자 채용</t>
+          <t>런드리24백엔드개발자</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>(주)포씨게이트</t>
+          <t>(주)의식주컴퍼니</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>경기군포시</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>~ 06/09(화)</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53847325&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53967438&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -8116,27 +8116,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>모바일 페이솔루션백엔드개발자(경력직)</t>
+          <t>백엔드개발자(4~6년)</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>주식회사아이닛</t>
+          <t>(주)에스피코리아</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울강서구</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>~ 06/25(목)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53817159&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0320add0-4559-4939-83ea-cd62c0ea4fa3</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53981282&amp;location=ts&amp;searchword=%EB%B0%B1%EC%97%94%EB%93%9C&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=0c37b1d4-4298-43b0-8ff1-63f52980b24a</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54044309&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54044309&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53970437&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53970437&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54058113&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54058113&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53756402&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53756402&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53878331&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53878331&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54063256&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54063256&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073720&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073720&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53733963&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53733963&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8404,27 +8404,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>데이터분석및 웹기획 담당자 채용</t>
+          <t>긴급) 데이터 전문가 (BI개발+데이터분석) - 글로벌TOP종합상사</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>(주)에듀캔버스</t>
+          <t>휴머레인컨설팅</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>경기성남시 수정구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>~ 06/13(토)</t>
+          <t>~ 06/21(일)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53625302&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54097349&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8436,27 +8436,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>데이터분석/BI 담당 (주임~대리)</t>
+          <t>데이터분석및 웹기획 담당자 채용</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>주식회사 리만코리아</t>
+          <t>(주)에듀캔버스</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기성남시 수정구</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>~ 06/17(수)</t>
+          <t>~ 06/13(토)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53919315&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53625302&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>AI데이터분석및 AI 활용 응용 프로그램개발</t>
+          <t>데이터분석/BI 담당 (주임~대리)</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>(주)아이티공간</t>
+          <t>주식회사 리만코리아</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>울산남구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>~ 06/21(일)</t>
+          <t>~ 06/17(수)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53969292&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53919315&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8500,27 +8500,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>데이터분석금융투자분석  투자경험 필요.  나이무관 파트가능</t>
+          <t>AI데이터분석및 AI 활용 응용 프로그램개발</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>제이투케이</t>
+          <t>(주)아이티공간</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>울산남구</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>~ 06/21(일)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53635768&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53969292&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8532,27 +8532,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>(주)스마트카라 CS팀(AS데이터분석) 부문 채용</t>
+          <t>데이터분석금융투자분석  투자경험 필요.  나이무관 파트가능</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>(주)스마트카라</t>
+          <t>제이투케이</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>인천연수구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53843552&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53635768&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8564,27 +8564,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[캐시워크]데이터분석담당 병역특례 대상자 모집</t>
+          <t>(주)스마트카라 CS팀(AS데이터분석) 부문 채용</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>넛지헬스케어(주)</t>
+          <t>(주)스마트카라</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>인천연수구</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>~ 07/21(화)</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53971489&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53843552&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8596,27 +8596,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>## 전기 충전 인프라 상장기업 -  가동률제고팀데이터분석가</t>
+          <t>[캐시워크]데이터분석담당 병역특례 대상자 모집</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>(주)백그라운드</t>
+          <t>넛지헬스케어(주)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>경기안양시 동안구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>~ 07/21(화)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53981901&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53971489&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>역삼동 위치 화장품, 생활용품기업데이터분석3-6년차</t>
+          <t>## 전기 충전 인프라 상장기업 -  가동률제고팀데이터분석가</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>한스컨설팅</t>
+          <t>(주)백그라운드</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기안양시 동안구</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54098370&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53981901&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>긴급) 데이터 전문가 (BI개발+데이터분석) - 글로벌TOP종합상사</t>
+          <t>역삼동 위치 화장품, 생활용품기업데이터분석3-6년차</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>휴머레인컨설팅</t>
+          <t>한스컨설팅</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>~ 06/21(일)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54097349&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54098370&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54015599&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54015599&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54036521&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54036521&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53847223&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53847223&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53983095&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53983095&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54053759&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54053759&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53931094&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53931094&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54056962&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54056962&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087188&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087188&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059278&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059278&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012358&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012358&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54076210&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54076210&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9044,27 +9044,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[ 한패스 ] HR Specialist - 채용 및 인사데이터 분석 경력 채용</t>
+          <t>[이노션] 데이터 분석 및 컨설팅 (Junior) (계약직)</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>한패스(주)</t>
+          <t>(주)이노션</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54044262&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54075360&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9076,27 +9076,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[유명외국계/복지우수] SCM/물류 데이터 분석 및 리포팅 담당</t>
+          <t>[ 한패스 ] HR Specialist - 채용 및 인사데이터 분석 경력 채용</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>(주)바른인사컨설팅</t>
+          <t>한패스(주)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079246&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54044262&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9108,27 +9108,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[통계팀] 데이터 분석가(사회조사분석사)</t>
+          <t>[유명외국계/복지우수] SCM/물류 데이터 분석 및 리포팅 담당</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>(주)한국정보통계</t>
+          <t>(주)바른인사컨설팅</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>전북전주시 완산구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>~ 07/31(금)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54049070&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079246&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9140,27 +9140,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>주)엔틀 에너지AI사업팀 데이터 분석 담당 채용(서울)</t>
+          <t>[통계팀] 데이터 분석가(사회조사분석사)</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>(주)엔틀</t>
+          <t>(주)한국정보통계</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>서울성동구</t>
+          <t>전북전주시 완산구</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 07/31(금)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54055210&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54049070&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>빅데이터 분석가 (신입 및 경력) 모집</t>
+          <t>주)엔틀 에너지AI사업팀 데이터 분석 담당 채용(서울)</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>바탕에비뉴(주)</t>
+          <t>(주)엔틀</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>서울구로구</t>
+          <t>서울성동구</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>~ 06/18(목)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53932017&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54055210&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9204,27 +9204,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[을지로] BC카드 데이터추출 및 분석 지원 담당 채용</t>
+          <t>빅데이터 분석가 (신입 및 경력) 모집</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>(주)케이티아이에스</t>
+          <t>바탕에비뉴(주)</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>서울중구</t>
+          <t>서울구로구</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/18(목)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53819392&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53932017&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9236,27 +9236,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[서울] ﻿AI 비전·데이터 분석 엔지니어</t>
+          <t>[을지로] BC카드 데이터추출 및 분석 지원 담당 채용</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>(주)인터엑스</t>
+          <t>(주)케이티아이에스</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>서울금천구</t>
+          <t>서울중구</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53829375&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53819392&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9268,27 +9268,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>(삼성동) 웹 데이터 분석, 컨설팅 모집 (신입, 경력)</t>
+          <t>[서울] ﻿AI 비전·데이터 분석 엔지니어</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>(주)엑셀리언트</t>
+          <t>(주)인터엑스</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울금천구</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>~ 06/14(일)</t>
+          <t>오늘마감</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53901896&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53829375&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9300,27 +9300,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>연구과제참여 - AI기반 의료 데이터(Image, EMR) 분석 채용</t>
+          <t>(삼성동) 웹 데이터 분석, 컨설팅 모집 (신입, 경력)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>(주)엑셀리언트</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>서울종로구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>~ 06/14(일)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53956888&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53901896&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9332,27 +9332,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[판교] 데이터 분석 플랫폼 및 대시보드 개발 운영 업무 채용</t>
+          <t>연구과제참여 - AI기반 의료 데이터(Image, EMR) 분석 채용</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>(주)에스이에스</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>경기성남시 수정구</t>
+          <t>서울종로구</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>~ 06/12(금)</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016530&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53956888&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9364,27 +9364,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>(주)장민이엔씨 기술연구소 AI 기반 데이터 분석 직원 채용</t>
+          <t>[판교] 데이터 분석 플랫폼 및 대시보드 개발 운영 업무 채용</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>장민이엔씨</t>
+          <t>(주)에스이에스</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>경기성남시 수정구</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>~ 06/30(화)</t>
+          <t>~ 06/12(금)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54076403&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016530&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9396,27 +9396,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>[티사이언티픽] 통계/데이터 분석 담당자</t>
+          <t>(주)장민이엔씨 기술연구소 AI 기반 데이터 분석 직원 채용</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>(주)티사이언티픽</t>
+          <t>장민이엔씨</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>전남나주시</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>~ 07/04(토)</t>
+          <t>~ 06/30(화)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54072742&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b9fa3a07-262f-4360-8687-f5e7c73939cd</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54076403&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=5c499429-fdce-4539-af79-248a40181d02</t>
         </is>
       </c>
     </row>
@@ -9428,27 +9428,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>기업부설연구소 AI 데이터 분석가</t>
+          <t>[티사이언티픽] 통계/데이터 분석 담당자</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>(주)이지수능교육</t>
+          <t>(주)티사이언티픽</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>전남나주시</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>~ 07/26(일)</t>
+          <t>~ 07/04(토)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004233&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54072742&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9460,27 +9460,27 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>[쿠팡·네이버 상품관리 MD] 데이터 분석 및 상품기획 담당 모집</t>
+          <t>기업부설연구소 AI 데이터 분석가</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>라이트밸런스(주)</t>
+          <t>(주)이지수능교육</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>경기오산시</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>~ 07/05(일)</t>
+          <t>~ 07/26(일)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087547&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54004233&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9492,27 +9492,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>심장 CT 영상데이터 분석가(방사선사) 채용</t>
+          <t>[쿠팡·네이버 상품관리 MD] 데이터 분석 및 상품기획 담당 모집</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>(주)온택트헬스</t>
+          <t>라이트밸런스(주)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>서울서대문구</t>
+          <t>경기오산시</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>~ 07/26(일)</t>
+          <t>~ 07/05(일)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54003302&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087547&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9524,27 +9524,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>휴먼 및 반려동물 마이크로바이옴 NGS 데이터 리포트 연구 분석</t>
+          <t>심장 CT 영상데이터 분석가(방사선사) 채용</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>(주)인크로비</t>
+          <t>(주)온택트헬스</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>서울금천구</t>
+          <t>서울서대문구</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>~ 07/11(토)</t>
+          <t>~ 07/26(일)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53865013&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54003302&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9556,27 +9556,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>데이터 분석/언더라이팅 정책 기획</t>
+          <t>휴먼 및 반려동물 마이크로바이옴 NGS 데이터 리포트 연구 분석</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>에이스아메리칸화재해상보험(주)</t>
+          <t>(주)인크로비</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>서울종로구</t>
+          <t>서울금천구</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>~ 06/13(토)</t>
+          <t>~ 07/11(토)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53902026&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53865013&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9588,27 +9588,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>[이노션] 데이터 분석 및 컨설팅 (Junior) (계약직)</t>
+          <t>데이터 분석/언더라이팅 정책 기획</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>(주)이노션</t>
+          <t>에이스아메리칸화재해상보험(주)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울종로구</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>~ 06/13(토)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54075360&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53902026&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53669263&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53669263&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016475&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016475&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53957116&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53957116&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53955590&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53955590&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53689411&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53689411&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54022705&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54022705&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012785&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012785&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060244&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54060244&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53819437&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53819437&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53980484&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53980484&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53829547&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53829547&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53942696&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53942696&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085618&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085618&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53901184&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53901184&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53879141&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53879141&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53954558&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53954558&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54061905&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54061905&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53984480&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53984480&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079954&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54079954&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53801181&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53801181&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54080051&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54080051&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10292,27 +10292,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>[에코마케팅]데이터 분석가(DA) 경력 채용</t>
+          <t>데이터 모델 및 분석 담당자 모집</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>(주)에코마케팅</t>
+          <t>(주)하이퍼정보</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>서울송파구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>~ 06/15(월)</t>
+          <t>~ 07/04(토)</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059304&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073601&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10324,27 +10324,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>데이터 분석가 채용</t>
+          <t>[에코마케팅]데이터 분석가(DA) 경력 채용</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>(주)온택트헬스</t>
+          <t>(주)에코마케팅</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>서울서대문구</t>
+          <t>서울송파구</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>~ 06/23(화)</t>
+          <t>~ 06/15(월)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53721937&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54059304&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10356,27 +10356,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>LC-MS / Metabolomics 데이터 처리 연구 분석가 모집</t>
+          <t>데이터 분석가 채용</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>(주)이빗</t>
+          <t>(주)온택트헬스</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울서대문구</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>~ 07/17(금)</t>
+          <t>~ 06/23(화)</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53920983&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53721937&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10388,12 +10388,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>[경력] AI기반 시계열 데이터 분석</t>
+          <t>LC-MS / Metabolomics 데이터 처리 연구 분석가 모집</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>(주)파인더스</t>
+          <t>(주)이빗</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>~ 06/18(목)</t>
+          <t>~ 07/17(금)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53935891&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53920983&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10420,27 +10420,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>[게임업계최상위] 게임 데이터 분석가</t>
+          <t>[경력] AI기반 시계열 데이터 분석</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>(주)지니어스</t>
+          <t>(주)파인더스</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>~ 06/18(목)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53971402&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53935891&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10452,27 +10452,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>(MNCs) 데이터 분석가</t>
+          <t>[게임업계최상위] 게임 데이터 분석가</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>제이앤피에이치알컨설팅</t>
+          <t>(주)지니어스</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>오늘마감</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54084664&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53971402&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10484,27 +10484,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>(주)노트스퀘어 빅데이터 분석 개발자 채용 공고</t>
+          <t>(MNCs) 데이터 분석가</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>(주)노트스퀘어</t>
+          <t>제이앤피에이치알컨설팅</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>서울마포구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53708732&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54084664&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10516,27 +10516,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>(주)골든플래닛 데이터 플로우 및 시스템 아키텍처 분석가 채용</t>
+          <t>(주)노트스퀘어 빅데이터 분석 개발자 채용 공고</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>(주)골든플래닛</t>
+          <t>(주)노트스퀘어</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울마포구</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53740707&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53708732&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10548,27 +10548,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>[NICE 지니데이타] 데이터 분석/가공 및 프로젝트 수행</t>
+          <t>(주)골든플래닛 데이터 플로우 및 시스템 아키텍처 분석가 채용</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>나이스지니데이타주식회사</t>
+          <t>(주)골든플래닛</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>~ 07/27(월)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010383&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53740707&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10580,27 +10580,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>[미리디] 데이터 분석팀 리드</t>
+          <t>[NICE 지니데이타] 데이터 분석/가공 및 프로젝트 수행</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>(주)미리디</t>
+          <t>나이스지니데이타주식회사</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>서울구로구</t>
+          <t>서울영등포구</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>~ 07/10(금)</t>
+          <t>~ 07/27(월)</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53849912&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010383&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10612,27 +10612,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>영업/마케팅 데이터 분석가(시각화) 채용</t>
+          <t>[미리디] 데이터 분석팀 리드</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>(주)디에스오토</t>
+          <t>(주)미리디</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>경기수원시 권선구</t>
+          <t>서울구로구</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>~ 06/10(수)</t>
+          <t>~ 07/10(금)</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53851944&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53849912&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10644,27 +10644,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>[디지털 마케팅] 마케팅 데이터 분석/비즈니스 분석 컨설턴트</t>
+          <t>영업/마케팅 데이터 분석가(시각화) 채용</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>(주)스카우트</t>
+          <t>(주)디에스오토</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기수원시 권선구</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/10(수)</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54057654&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53851944&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>[디지털 마케팅] 디지털 플랫폼 데이터 분석 컨설턴트</t>
+          <t>[디지털 마케팅] 마케팅 데이터 분석/비즈니스 분석 컨설턴트</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54057660&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=a075d556-4db6-43c5-a7e6-4bd02af2007b</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54057654&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=34b65929-691a-44ae-a8a0-e9e5a2074688</t>
         </is>
       </c>
     </row>
@@ -10708,27 +10708,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>[유명 금융 IT대기업] 비즈니스 데이터 분석 실장</t>
+          <t>[디지털 마케팅] 디지털 플랫폼 데이터 분석 컨설턴트</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>(주)리앤파트너</t>
+          <t>(주)스카우트</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087376&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54057660&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10740,27 +10740,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>빅테크 데이터 분석 실장급 채용</t>
+          <t>[유명 금융 IT대기업] 비즈니스 데이터 분석 실장</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>리뉴피플 주식회사</t>
+          <t>(주)리앤파트너</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085382&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54087376&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10772,27 +10772,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>데이터 분석( SQL, Python) FPS게임/세계적게임사</t>
+          <t>빅테크 데이터 분석 실장급 채용</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>(주)에이치알비즈코리아</t>
+          <t>리뉴피플 주식회사</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>~ 06/15(월)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54037712&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54085382&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10804,12 +10804,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>고객 행동 데이터 분석가</t>
+          <t>데이터 분석( SQL, Python) FPS게임/세계적게임사</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>(주)올빅뎃</t>
+          <t>(주)에이치알비즈코리아</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/15(월)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010883&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54037712&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10836,27 +10836,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>[병특 전문연] (주)일루넥스 인공지능, 빅데이터 분석 분야 채용</t>
+          <t>고객 행동 데이터 분석가</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>일루넥스</t>
+          <t>(주)올빅뎃</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>경기고양시 덕양구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53636938&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54010883&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10868,27 +10868,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>[대형 핀테크 기업] 그로스 데이터 분석 담당자</t>
+          <t>[병특 전문연] (주)일루넥스 인공지능, 빅데이터 분석 분야 채용</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>주) 석세스코리아컨설팅</t>
+          <t>일루넥스</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기고양시 덕양구</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>~ 06/12(금)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012851&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53636938&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>[국내탑 암호화폐거래소] 그로스데이터 분석</t>
+          <t>[대형 핀테크 기업] 그로스 데이터 분석 담당자</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016361&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54012851&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10932,27 +10932,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>[유명 금융 IT대기업] 그로스 데이터 분석 담당자</t>
+          <t>[국내탑 암호화폐거래소] 그로스데이터 분석</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>(주)리앤파트너</t>
+          <t>주) 석세스코리아컨설팅</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>~ 06/11(목)</t>
+          <t>~ 06/12(금)</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54007141&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54016361&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>[유명 금융 IT대기업] 비즈니스 데이터 분석</t>
+          <t>[유명 금융 IT대기업] 그로스 데이터 분석 담당자</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>~ 06/16(화)</t>
+          <t>~ 06/11(목)</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54039970&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54007141&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -10996,17 +10996,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>게임 데이터 분석가/Python/R을 활용/세계적게임사</t>
+          <t>[유명 금융 IT대기업] 비즈니스 데이터 분석</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>(주)에이치알비즈코리아</t>
+          <t>(주)리앤파트너</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046417&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54039970&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11028,27 +11028,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>데이터 분석 경력자 (총괄 리더)-국내 핀테크 유니콘 기업</t>
+          <t>게임 데이터 분석가/Python/R을 활용/세계적게임사</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>(주)에이치알원컨설팅</t>
+          <t>(주)에이치알비즈코리아</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>서울마포구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/16(화)</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54089803&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54046417&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>데이터 분석 경험자-국내 핀테크 유니콘 기업</t>
+          <t>데이터 분석 경력자 (총괄 리더)-국내 핀테크 유니콘 기업</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54089850&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54089803&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11092,27 +11092,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>[글로벌바이오리서치] Senior Data Analyst 데이터 분석</t>
+          <t>데이터 분석 경험자-국내 핀테크 유니콘 기업</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>글로벌바이오리서치</t>
+          <t>(주)에이치알원컨설팅</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>서울중구</t>
+          <t>서울마포구</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>~ 06/18(목)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53868316&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54089850&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>국내 대기업 - 데이터 분석 전문가 경력직</t>
+          <t>[글로벌바이오리서치] Senior Data Analyst 데이터 분석</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>(주)커리어앤스카우트</t>
+          <t>글로벌바이오리서치</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54093127&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53868316&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11156,27 +11156,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>[데이콘인피니티] 데이터 분석 전문 컨설턴트</t>
+          <t>국내 대기업 - 데이터 분석 전문가 경력직</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>(주)데이콘인피니티</t>
+          <t>(주)커리어앤스카우트</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>서울영등포구</t>
+          <t>서울중구</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>~ 07/02(목)</t>
+          <t>~ 06/18(목)</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54055021&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54093127&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11188,27 +11188,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>빅데이터 기반 마케팅광고 성과분석 강사님채용(마케팅 가능자)</t>
+          <t>[데이콘인피니티] 데이터 분석 전문 컨설턴트</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>(주)이젠컴퓨터아카데미안산</t>
+          <t>(주)데이콘인피니티</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>경기안산시 상록구</t>
+          <t>서울영등포구</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>~ 06/27(토)</t>
+          <t>~ 07/02(목)</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54013635&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54055021&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11220,27 +11220,27 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>[삼양식품] 커머셜 마케팅 데이터 분석 파트장/매니저</t>
+          <t>빅데이터 기반 마케팅광고 성과분석 강사님채용(마케팅 가능자)</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>삼양라운드스퀘어(주)</t>
+          <t>(주)이젠컴퓨터아카데미안산</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>서울중구</t>
+          <t>경기안산시 상록구</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/27(토)</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53659816&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54013635&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11252,27 +11252,27 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>WANTED: 데이터 플로우 및 시스템 아키텍처 분석 경력자</t>
+          <t>[삼양식품] 커머셜 마케팅 데이터 분석 파트장/매니저</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>퍼스트브레인INT</t>
+          <t>삼양라운드스퀘어(주)</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>서울중구</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>~ 06/19(금)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078239&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53659816&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11284,27 +11284,27 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>데이터 분석가(자사몰·마케팅·세일즈) 채용</t>
+          <t>WANTED: 데이터 플로우 및 시스템 아키텍처 분석 경력자</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>(주)디에스오토네트웍스</t>
+          <t>퍼스트브레인INT</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>서울서초구</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>~ 06/20(토)</t>
+          <t>~ 06/19(금)</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53677048&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54078239&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11316,12 +11316,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>[글로빛논문컨설팅] 빅데이터 분석,AI(머신러닝,딥러닝)박사</t>
+          <t>데이터 분석가(자사몰·마케팅·세일즈) 채용</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>글로빛(주)</t>
+          <t>(주)디에스오토네트웍스</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>~ 06/20(토)</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53790886&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53677048&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11348,27 +11348,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>[플랫폼본부] 데이터 분석가</t>
+          <t>[글로빛논문컨설팅] 빅데이터 분석,AI(머신러닝,딥러닝)박사</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>(주)넥슨코리아</t>
+          <t>글로빛(주)</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>경기성남시 분당구</t>
+          <t>서울서초구</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>~ 06/15(월)</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53078333&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53790886&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11380,27 +11380,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>(주)엔텔스 AI모델 개발 &amp; 데이터 분석 전문가 채용(경력)</t>
+          <t>[플랫폼본부] 데이터 분석가</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>(주)엔텔스</t>
+          <t>(주)넥슨코리아</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기성남시 분당구</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>~ 06/15(월)</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53861151&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53078333&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11412,27 +11412,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>보안 데이터 분석 엔지니어 채용 (SIEM/SOAR/Senior)</t>
+          <t>(주)엔텔스 AI모델 개발 &amp; 데이터 분석 전문가 채용(경력)</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>메가존클라우드(주)</t>
+          <t>(주)엔텔스</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>경기과천시</t>
+          <t>서울강남구</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>상시채용</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53687903&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53861151&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>빅데이터 플랫폼 구축 (분석/설계/개발/PL)</t>
+          <t>보안 데이터 분석 엔지니어 채용 (SIEM/SOAR/Senior)</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>(주)스카우트</t>
+          <t>메가존클라우드(주)</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>서울강남구</t>
+          <t>경기과천시</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>채용시</t>
+          <t>상시채용</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54042365&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53687903&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11476,12 +11476,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>데이터 모델 및 분석 담당자 모집</t>
+          <t>빅데이터 플랫폼 구축 (분석/설계/개발/PL)</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>(주)하이퍼정보</t>
+          <t>(주)스카우트</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>~ 07/04(토)</t>
+          <t>채용시</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54073601&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54042365&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54013582&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54013582&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53831286&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53831286&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54017378&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54017378&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53647845&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53647845&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54098389&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54098389&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54080007&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54080007&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53862718&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53862718&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53861949&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53861949&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53855255&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53855255&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038278&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038278&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038370&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038370&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038086&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038086&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038214&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038214&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53815440&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=53815440&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038205&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=b0185c37-835d-47ab-8d53-6ae546c8bd12</t>
+          <t>https://www.saramin.co.kr/zf_user/jobs/relay/view?view_type=search&amp;rec_idx=54038205&amp;location=ts&amp;searchword=%EB%8D%B0%EC%9D%B4%ED%84%B0%EB%B6%84%EC%84%9D&amp;searchType=search&amp;paid_fl=n&amp;search_uuid=1db9841e-cb57-4127-aa75-3989a3e86644</t>
         </is>
       </c>
     </row>
